--- a/grupos/3ALCM - Estadisticos 20241.xlsx
+++ b/grupos/3ALCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -209,15 +209,15 @@
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
@@ -239,63 +239,75 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ALTAMIRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>AZPIRI</t>
   </si>
   <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RICO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>ROMAN</t>
   </si>
   <si>
@@ -305,132 +317,159 @@
     <t>SEGURA</t>
   </si>
   <si>
-    <t>TEXOCO</t>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>YOPIHUA</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
     <t>CAMARILLO</t>
   </si>
   <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
     <t>TELLEZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>MIXTECO</t>
   </si>
   <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>ARIADNA JARETZI</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>LINET</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
     <t>XIMENA</t>
   </si>
   <si>
+    <t>ANGEL NAIN</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>OSWALDO</t>
+  </si>
+  <si>
     <t>JANETH</t>
   </si>
   <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>DAYANA ASTRID</t>
+  </si>
+  <si>
     <t>MARIAM MICHAELL</t>
   </si>
   <si>
+    <t>LAURA ISABEL</t>
+  </si>
+  <si>
     <t>YAMILET</t>
   </si>
   <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
     <t>ALEX TADEO</t>
   </si>
   <si>
+    <t>YEIMI ALEXANDER</t>
+  </si>
+  <si>
     <t>ANGEL EDUC</t>
   </si>
   <si>
+    <t>AXEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>REY</t>
+  </si>
+  <si>
+    <t>ARELI DANAE</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>ANIELA SAMANTA</t>
   </si>
   <si>
-    <t>LINET</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>OSWALDO</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>DAYANA ASTRID</t>
-  </si>
-  <si>
-    <t>LAURA ISABEL</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>YEIMI ALEXANDER</t>
-  </si>
-  <si>
-    <t>AXEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>ARELI DANAE</t>
-  </si>
-  <si>
     <t>CONCEPCION GUADALUPE</t>
   </si>
   <si>
@@ -440,7 +479,10 @@
     <t>DAFNE</t>
   </si>
   <si>
-    <t>ARIADNA JARETZI</t>
+    <t>HEIDI</t>
+  </si>
+  <si>
+    <t>ALDO</t>
   </si>
   <si>
     <t>GUADALUPE ANAHI</t>
@@ -989,28 +1031,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1040,10 +1082,10 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -1090,28 +1132,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1191,28 +1233,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1239,22 +1281,22 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6">
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF6">
         <v>9</v>
@@ -1292,28 +1334,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1340,19 +1382,19 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE7">
         <v>7</v>
@@ -1393,28 +1435,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1441,22 +1483,22 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>5</v>
       </c>
       <c r="AB8">
+        <v>8</v>
+      </c>
+      <c r="AC8">
         <v>6</v>
       </c>
-      <c r="AC8">
+      <c r="AD8">
+        <v>8</v>
+      </c>
+      <c r="AE8">
         <v>5</v>
-      </c>
-      <c r="AD8">
-        <v>6</v>
-      </c>
-      <c r="AE8">
-        <v>6</v>
       </c>
       <c r="AF8">
         <v>9</v>
@@ -1494,28 +1536,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1548,13 +1590,13 @@
         <v>10</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>10</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE9">
         <v>9</v>
@@ -1595,28 +1637,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1655,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="AD10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE10">
         <v>9</v>
@@ -1696,28 +1738,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1750,13 +1792,13 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE11">
         <v>9</v>
@@ -1797,28 +1839,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1851,16 +1893,16 @@
         <v>9</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>10</v>
       </c>
       <c r="AE12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF12">
         <v>10</v>
@@ -1898,28 +1940,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1952,10 +1994,10 @@
         <v>9</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD13">
         <v>10</v>
@@ -1999,28 +2041,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -2047,22 +2089,22 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF14">
         <v>8</v>
@@ -2100,28 +2142,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2157,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD15">
         <v>10</v>
@@ -2201,28 +2243,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2252,7 +2294,7 @@
         <v>9</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>5</v>
@@ -2264,7 +2306,7 @@
         <v>10</v>
       </c>
       <c r="AE16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF16">
         <v>9</v>
@@ -2302,28 +2344,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2350,19 +2392,19 @@
         <v>-1</v>
       </c>
       <c r="Z17">
+        <v>8</v>
+      </c>
+      <c r="AA17">
         <v>7</v>
       </c>
-      <c r="AA17">
-        <v>5</v>
-      </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE17">
         <v>7</v>
@@ -2403,28 +2445,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2451,19 +2493,19 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA18">
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE18">
         <v>10</v>
@@ -2504,28 +2546,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2552,7 +2594,7 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2561,7 +2603,7 @@
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD19">
         <v>10</v>
@@ -2605,28 +2647,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2659,16 +2701,16 @@
         <v>10</v>
       </c>
       <c r="AB20">
+        <v>8</v>
+      </c>
+      <c r="AC20">
         <v>7</v>
       </c>
-      <c r="AC20">
-        <v>6</v>
-      </c>
       <c r="AD20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF20">
         <v>9</v>
@@ -2706,28 +2748,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2754,25 +2796,25 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA21">
+        <v>7</v>
+      </c>
+      <c r="AB21">
+        <v>7</v>
+      </c>
+      <c r="AC21">
+        <v>10</v>
+      </c>
+      <c r="AD21">
+        <v>8</v>
+      </c>
+      <c r="AE21">
         <v>5</v>
       </c>
-      <c r="AB21">
-        <v>5</v>
-      </c>
-      <c r="AC21">
-        <v>10</v>
-      </c>
-      <c r="AD21">
-        <v>6</v>
-      </c>
-      <c r="AE21">
-        <v>6</v>
-      </c>
       <c r="AF21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG21">
         <v>-1</v>
@@ -2807,28 +2849,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2861,13 +2903,13 @@
         <v>9</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE22">
         <v>5</v>
@@ -2908,28 +2950,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2962,13 +3004,13 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE23">
         <v>10</v>
@@ -3009,28 +3051,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -3057,13 +3099,13 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -3072,7 +3114,7 @@
         <v>10</v>
       </c>
       <c r="AE24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF24">
         <v>9</v>
@@ -3110,28 +3152,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3164,13 +3206,13 @@
         <v>9</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>7</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE25">
         <v>10</v>
@@ -3211,28 +3253,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3259,19 +3301,19 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA26">
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE26">
         <v>10</v>
@@ -3312,28 +3354,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3363,19 +3405,19 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>9</v>
       </c>
       <c r="AD27">
+        <v>8</v>
+      </c>
+      <c r="AE27">
         <v>6</v>
-      </c>
-      <c r="AE27">
-        <v>7</v>
       </c>
       <c r="AF27">
         <v>10</v>
@@ -3413,28 +3455,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3464,16 +3506,16 @@
         <v>10</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE28">
         <v>9</v>
@@ -3514,28 +3556,28 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3562,7 +3604,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>8</v>
@@ -3577,7 +3619,7 @@
         <v>6</v>
       </c>
       <c r="AE29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF29">
         <v>8</v>
@@ -3615,28 +3657,28 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3666,16 +3708,16 @@
         <v>9</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE30">
         <v>7</v>
@@ -3716,28 +3758,28 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3817,28 +3859,28 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3865,19 +3907,19 @@
         <v>-1</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE32">
         <v>9</v>
@@ -3918,28 +3960,28 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3972,13 +4014,13 @@
         <v>9</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE33">
         <v>10</v>
@@ -4019,28 +4061,28 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -4067,19 +4109,19 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE34">
         <v>9</v>
@@ -4120,28 +4162,28 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4168,22 +4210,22 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA35">
+        <v>8</v>
+      </c>
+      <c r="AB35">
         <v>7</v>
       </c>
-      <c r="AB35">
-        <v>6</v>
-      </c>
       <c r="AC35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF35">
         <v>10</v>
@@ -4221,28 +4263,28 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4269,25 +4311,25 @@
         <v>-1</v>
       </c>
       <c r="Z36">
+        <v>8</v>
+      </c>
+      <c r="AA36">
         <v>7</v>
       </c>
-      <c r="AA36">
-        <v>5</v>
-      </c>
       <c r="AB36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE36">
         <v>5</v>
       </c>
       <c r="AF36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG36">
         <v>-1</v>
@@ -4322,28 +4364,28 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4370,22 +4412,22 @@
         <v>-1</v>
       </c>
       <c r="Z37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA37">
         <v>5</v>
       </c>
       <c r="AB37">
+        <v>7</v>
+      </c>
+      <c r="AC37">
         <v>5</v>
       </c>
-      <c r="AC37">
+      <c r="AD37">
+        <v>8</v>
+      </c>
+      <c r="AE37">
         <v>6</v>
-      </c>
-      <c r="AD37">
-        <v>6</v>
-      </c>
-      <c r="AE37">
-        <v>7</v>
       </c>
       <c r="AF37">
         <v>9</v>
@@ -4423,28 +4465,28 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4471,22 +4513,22 @@
         <v>-1</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA38">
         <v>9</v>
       </c>
       <c r="AB38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD38">
         <v>10</v>
       </c>
       <c r="AE38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF38">
         <v>10</v>
@@ -4524,28 +4566,28 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -4575,19 +4617,19 @@
         <v>9</v>
       </c>
       <c r="AA39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB39">
+        <v>9</v>
+      </c>
+      <c r="AC39">
+        <v>9</v>
+      </c>
+      <c r="AD39">
+        <v>10</v>
+      </c>
+      <c r="AE39">
         <v>7</v>
-      </c>
-      <c r="AC39">
-        <v>9</v>
-      </c>
-      <c r="AD39">
-        <v>9</v>
-      </c>
-      <c r="AE39">
-        <v>8</v>
       </c>
       <c r="AF39">
         <v>10</v>
@@ -4916,10 +4958,10 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L6">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M6">
         <v>94.3</v>
@@ -4928,10 +4970,10 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4940,10 +4982,10 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="T6">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U6">
         <v>94.3</v>
@@ -4952,10 +4994,10 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X6">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Y6">
         <v>100</v>
@@ -4993,19 +5035,19 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -5017,19 +5059,19 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V7">
         <v>100</v>
       </c>
       <c r="W7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X7">
         <v>100</v>
@@ -5070,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L8">
         <v>96</v>
@@ -5082,7 +5124,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -5094,7 +5136,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="T8">
         <v>96</v>
@@ -5106,7 +5148,7 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X8">
         <v>100</v>
@@ -5147,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -5171,7 +5213,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -5224,7 +5266,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -5236,10 +5278,10 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -5248,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -5260,10 +5302,10 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -5301,7 +5343,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -5325,7 +5367,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -5378,7 +5420,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -5402,7 +5444,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -5470,7 +5512,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -5494,7 +5536,7 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -5532,7 +5574,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -5544,7 +5586,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -5556,7 +5598,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -5568,7 +5610,7 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X14">
         <v>100</v>
@@ -5621,7 +5663,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -5645,7 +5687,7 @@
         <v>100</v>
       </c>
       <c r="W15">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X15">
         <v>100</v>
@@ -5689,19 +5731,19 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M16">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -5713,19 +5755,19 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="U16">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V16">
         <v>100</v>
       </c>
       <c r="W16">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X16">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -5763,7 +5805,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -5775,7 +5817,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -5787,7 +5829,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -5799,7 +5841,7 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="X17">
         <v>100</v>
@@ -5840,7 +5882,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -5852,7 +5894,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -5864,7 +5906,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -5876,7 +5918,7 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X18">
         <v>100</v>
@@ -5923,13 +5965,13 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -5947,13 +5989,13 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="V19">
         <v>100</v>
       </c>
       <c r="W19">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -5994,7 +6036,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -6006,10 +6048,10 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -6018,7 +6060,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -6030,10 +6072,10 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X20">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -6071,22 +6113,22 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L21">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N21">
         <v>100</v>
       </c>
       <c r="O21">
-        <v>77.8</v>
+        <v>84.8</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -6095,22 +6137,22 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T21">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V21">
         <v>100</v>
       </c>
       <c r="W21">
-        <v>77.8</v>
+        <v>84.8</v>
       </c>
       <c r="X21">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Y21">
         <v>100</v>
@@ -6148,7 +6190,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -6172,7 +6214,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -6237,7 +6279,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -6261,7 +6303,7 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -6302,7 +6344,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -6317,7 +6359,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -6326,7 +6368,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -6341,7 +6383,7 @@
         <v>100</v>
       </c>
       <c r="X24">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Y24">
         <v>100</v>
@@ -6459,10 +6501,10 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -6483,10 +6525,10 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -6533,7 +6575,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -6545,7 +6587,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -6557,7 +6599,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -6569,7 +6611,7 @@
         <v>100</v>
       </c>
       <c r="W27">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X27">
         <v>100</v>
@@ -6610,7 +6652,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -6622,7 +6664,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -6634,7 +6676,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T28">
         <v>100</v>
@@ -6646,7 +6688,7 @@
         <v>100</v>
       </c>
       <c r="W28">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X28">
         <v>100</v>
@@ -6687,19 +6729,19 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L29">
         <v>94</v>
       </c>
       <c r="M29">
-        <v>94.3</v>
+        <v>90</v>
       </c>
       <c r="N29">
         <v>100</v>
       </c>
       <c r="O29">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -6711,19 +6753,19 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T29">
         <v>94</v>
       </c>
       <c r="U29">
-        <v>94.3</v>
+        <v>90</v>
       </c>
       <c r="V29">
         <v>100</v>
       </c>
       <c r="W29">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X29">
         <v>100</v>
@@ -6764,10 +6806,10 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -6776,7 +6818,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6788,10 +6830,10 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="T30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -6800,7 +6842,7 @@
         <v>100</v>
       </c>
       <c r="W30">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -6841,7 +6883,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -6865,7 +6907,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -6918,7 +6960,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -6942,7 +6984,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -7078,13 +7120,13 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N34">
         <v>100</v>
       </c>
       <c r="O34">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -7102,13 +7144,13 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V34">
         <v>100</v>
       </c>
       <c r="W34">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X34">
         <v>100</v>
@@ -7149,22 +7191,22 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="N35">
         <v>100</v>
       </c>
       <c r="O35">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P35">
-        <v>91.7</v>
+        <v>95.2</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -7173,22 +7215,22 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T35">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U35">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V35">
         <v>100</v>
       </c>
       <c r="W35">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X35">
-        <v>91.7</v>
+        <v>95.2</v>
       </c>
       <c r="Y35">
         <v>100</v>
@@ -7232,16 +7274,16 @@
         <v>96</v>
       </c>
       <c r="M36">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="N36">
         <v>100</v>
       </c>
       <c r="O36">
-        <v>88.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="P36">
-        <v>91.7</v>
+        <v>85.7</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -7256,16 +7298,16 @@
         <v>96</v>
       </c>
       <c r="U36">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="V36">
         <v>100</v>
       </c>
       <c r="W36">
-        <v>88.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="X36">
-        <v>91.7</v>
+        <v>85.7</v>
       </c>
       <c r="Y36">
         <v>100</v>
@@ -7303,7 +7345,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L37">
         <v>96</v>
@@ -7315,7 +7357,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -7327,7 +7369,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T37">
         <v>96</v>
@@ -7339,7 +7381,7 @@
         <v>100</v>
       </c>
       <c r="W37">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X37">
         <v>100</v>
@@ -7380,7 +7422,7 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -7404,7 +7446,7 @@
         <v>100</v>
       </c>
       <c r="S38">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T38">
         <v>100</v>
@@ -7457,7 +7499,7 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -7469,7 +7511,7 @@
         <v>100</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -7481,7 +7523,7 @@
         <v>100</v>
       </c>
       <c r="S39">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="T39">
         <v>100</v>
@@ -7493,7 +7535,7 @@
         <v>100</v>
       </c>
       <c r="W39">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X39">
         <v>100</v>
@@ -7585,7 +7627,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -7594,19 +7636,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>63.9</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>36.1</v>
+        <v>11.1</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7620,25 +7662,25 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>80.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>19.4</v>
+        <v>11.1</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7652,25 +7694,25 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>86.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>13.9</v>
+        <v>5.6</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7681,28 +7723,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>36</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7734,7 +7776,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7766,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7798,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7848,7 +7890,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7880,19 +7922,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920079</v>
+        <v>23330051920251</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
@@ -7903,16 +7945,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920079</v>
+        <v>23330051920251</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -7926,19 +7968,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920086</v>
+        <v>23330051920097</v>
       </c>
       <c r="B4" t="s">
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>63</v>
@@ -7949,16 +7991,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920086</v>
+        <v>23330051920097</v>
       </c>
       <c r="B5" t="s">
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -7972,22 +8014,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920088</v>
+        <v>23330051920111</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7995,16 +8037,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920088</v>
+        <v>23330051920111</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -8018,22 +8060,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920090</v>
+        <v>23330051920112</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8041,16 +8083,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920090</v>
+        <v>23330051920112</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -8064,39 +8106,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920234</v>
+        <v>23330051920078</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920234</v>
+        <v>23330051920077</v>
       </c>
       <c r="B11" t="s">
         <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -8110,39 +8152,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920099</v>
+        <v>23330051920079</v>
       </c>
       <c r="B12" t="s">
         <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920099</v>
+        <v>23330051920080</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -8156,39 +8198,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920104</v>
+        <v>23330051920082</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920104</v>
+        <v>23330051920085</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -8202,39 +8244,39 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920261</v>
+        <v>23330051920086</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920261</v>
+        <v>23330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -8248,16 +8290,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920078</v>
+        <v>23330051920087</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -8271,16 +8313,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920077</v>
+        <v>23330051920088</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -8294,16 +8336,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920082</v>
+        <v>23330051920089</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -8317,16 +8359,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920085</v>
+        <v>23330051920090</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -8340,16 +8382,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920084</v>
+        <v>23330051920091</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
@@ -8363,16 +8405,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920087</v>
+        <v>23330051920234</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -8386,16 +8428,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920089</v>
+        <v>23330051920094</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -8409,16 +8451,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920091</v>
+        <v>23330051920099</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
@@ -8432,16 +8474,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920094</v>
+        <v>23330051920098</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -8455,16 +8497,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920098</v>
+        <v>23330051920100</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
@@ -8478,16 +8520,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920100</v>
+        <v>23330051920102</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -8501,16 +8543,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920102</v>
+        <v>23330051920103</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E29" t="s">
         <v>12</v>
@@ -8524,16 +8566,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920103</v>
+        <v>23330051920104</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
@@ -8547,16 +8589,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920106</v>
+        <v>23330051920261</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
@@ -8570,16 +8612,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920107</v>
+        <v>23330051920106</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
         <v>12</v>
@@ -8593,16 +8635,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920108</v>
+        <v>23330051920107</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
         <v>12</v>
@@ -8616,16 +8658,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920111</v>
+        <v>23330051920108</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
@@ -8639,16 +8681,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920115</v>
+        <v>23330051920110</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
@@ -8657,6 +8699,52 @@
         <v>62</v>
       </c>
       <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>23330051920114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>23330051920115</v>
+      </c>
+      <c r="B37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ALCM - Estadisticos 20241.xlsx
+++ b/grupos/3ALCM - Estadisticos 20241.xlsx
@@ -212,18 +212,18 @@
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -239,70 +239,70 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>MELANY</t>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ARIADNA JARETZI</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
   </si>
   <si>
     <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>ARIADNA JARETZI</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
   </si>
 </sst>
 </file>
@@ -850,10 +850,10 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -862,13 +862,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -889,7 +889,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -939,10 +939,10 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -951,13 +951,13 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1028,10 +1028,10 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1040,13 +1040,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1117,10 +1117,10 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1129,13 +1129,13 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1206,10 +1206,10 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1218,19 +1218,19 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1239,7 +1239,7 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -1295,10 +1295,10 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1307,19 +1307,19 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1384,10 +1384,10 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1396,13 +1396,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1417,7 +1417,7 @@
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>9</v>
@@ -1473,10 +1473,10 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1485,13 +1485,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1562,10 +1562,10 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1574,19 +1574,19 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1651,10 +1651,10 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1663,13 +1663,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1684,7 +1684,7 @@
         <v>9</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -1740,10 +1740,10 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1752,13 +1752,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1829,10 +1829,10 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1841,13 +1841,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1918,10 +1918,10 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1930,13 +1930,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1957,7 +1957,7 @@
         <v>7</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2007,10 +2007,10 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2019,13 +2019,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2040,13 +2040,13 @@
         <v>8</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>7</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2096,10 +2096,10 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2108,13 +2108,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2135,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2185,10 +2185,10 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2197,13 +2197,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2274,10 +2274,10 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2286,19 +2286,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2363,10 +2363,10 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2375,19 +2375,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2452,10 +2452,10 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2464,16 +2464,16 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2541,10 +2541,10 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2553,13 +2553,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2630,10 +2630,10 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2642,16 +2642,16 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2719,10 +2719,10 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2731,13 +2731,13 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2808,10 +2808,10 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2820,13 +2820,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2897,10 +2897,10 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2909,16 +2909,16 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2930,7 +2930,7 @@
         <v>9</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>6</v>
@@ -2986,10 +2986,10 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2998,13 +2998,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -3019,7 +3019,7 @@
         <v>8</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3075,10 +3075,10 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3087,19 +3087,19 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -3164,10 +3164,10 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3176,13 +3176,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3253,10 +3253,10 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3265,13 +3265,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3342,10 +3342,10 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3354,13 +3354,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3431,10 +3431,10 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3443,13 +3443,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3520,10 +3520,10 @@
         <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3532,13 +3532,13 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3609,10 +3609,10 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3621,19 +3621,19 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>-1</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>7</v>
@@ -3642,13 +3642,13 @@
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>7</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3698,10 +3698,10 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3710,19 +3710,19 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>8</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3787,10 +3787,10 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3799,19 +3799,19 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>8</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -3876,10 +3876,10 @@
         <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3888,16 +3888,16 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>-1</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>9</v>
@@ -3965,10 +3965,10 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3977,13 +3977,13 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>9</v>
@@ -3998,7 +3998,7 @@
         <v>9</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB39">
         <v>7</v>
@@ -4315,7 +4315,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R6">
         <v>95</v>
@@ -4330,7 +4330,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="V6">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4383,7 +4383,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4451,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R8">
         <v>96</v>
@@ -4519,7 +4519,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4587,7 +4587,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4602,7 +4602,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="V10">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4655,7 +4655,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4723,7 +4723,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4806,7 +4806,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4859,7 +4859,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -5010,7 +5010,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V16">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5063,7 +5063,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -5131,7 +5131,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -5267,7 +5267,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -5282,7 +5282,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="V20">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5332,10 +5332,10 @@
         <v>95.2</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q21">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R21">
         <v>94</v>
@@ -5350,7 +5350,7 @@
         <v>84.8</v>
       </c>
       <c r="V21">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5403,7 +5403,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5554,7 +5554,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5740,10 +5740,10 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>82.8</v>
       </c>
       <c r="Q27">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5811,7 +5811,7 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5876,10 +5876,10 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q29">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R29">
         <v>94</v>
@@ -5947,7 +5947,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="R30">
         <v>98</v>
@@ -6015,7 +6015,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -6083,7 +6083,7 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -6284,10 +6284,10 @@
         <v>95.2</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>82.8</v>
       </c>
       <c r="Q35">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R35">
         <v>98</v>
@@ -6302,7 +6302,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V35">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6370,7 +6370,7 @@
         <v>81.8</v>
       </c>
       <c r="V36">
-        <v>85.7</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6423,7 +6423,7 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R37">
         <v>96</v>
@@ -6491,7 +6491,7 @@
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R38">
         <v>100</v>
@@ -6559,7 +6559,7 @@
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -6695,10 +6695,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>36</v>
@@ -6716,7 +6716,7 @@
         <v>5.6</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6727,10 +6727,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>36</v>
@@ -6748,7 +6748,7 @@
         <v>5.6</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6780,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6791,7 +6791,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6823,7 +6823,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920081</v>
+        <v>23330051920105</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
@@ -6958,7 +6958,7 @@
         <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920081</v>
+        <v>23330051920105</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
@@ -6981,10 +6981,10 @@
         <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6992,19 +6992,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920230</v>
+        <v>23330051920105</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>63</v>
@@ -7027,7 +7027,7 @@
         <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>63</v>
@@ -7038,19 +7038,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920105</v>
+        <v>23330051920230</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>63</v>
@@ -7061,7 +7061,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920105</v>
+        <v>23330051920097</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
@@ -7073,10 +7073,10 @@
         <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7084,22 +7084,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920113</v>
+        <v>23330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7107,7 +7107,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920113</v>
+        <v>23330051920081</v>
       </c>
       <c r="B9" t="s">
         <v>76</v>
@@ -7119,10 +7119,10 @@
         <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7153,7 +7153,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920097</v>
+        <v>23330051920111</v>
       </c>
       <c r="B11" t="s">
         <v>78</v>
@@ -7165,10 +7165,10 @@
         <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7176,22 +7176,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920111</v>
+        <v>23330051920112</v>
       </c>
       <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
         <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7199,22 +7199,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920112</v>
+        <v>23330051920113</v>
       </c>
       <c r="B13" t="s">
         <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
         <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>

--- a/grupos/3ALCM - Estadisticos 20241.xlsx
+++ b/grupos/3ALCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="82">
   <si>
     <t>Materia</t>
   </si>
@@ -206,24 +206,24 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -239,70 +239,31 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>BAEZ</t>
+    <t>ABRIL</t>
   </si>
   <si>
     <t>MELANY</t>
   </si>
   <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
     <t>ARIADNA JARETZI</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
   </si>
 </sst>
 </file>
@@ -856,16 +817,16 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -877,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>8</v>
@@ -945,16 +906,16 @@
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1034,16 +995,16 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1055,16 +1016,16 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1123,16 +1084,16 @@
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1144,16 +1105,16 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1212,16 +1173,16 @@
         <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1233,16 +1194,16 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8">
         <v>9</v>
@@ -1301,16 +1262,16 @@
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1390,16 +1351,16 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1479,16 +1440,16 @@
         <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1568,16 +1529,16 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1657,16 +1618,16 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1746,16 +1707,16 @@
         <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1767,16 +1728,16 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1835,16 +1796,16 @@
         <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1856,7 +1817,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z15">
         <v>9</v>
@@ -1924,16 +1885,16 @@
         <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -1945,10 +1906,10 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2013,16 +1974,16 @@
         <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2102,16 +2063,16 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2191,16 +2152,16 @@
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2280,16 +2241,16 @@
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2369,16 +2330,16 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2393,13 +2354,13 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA21">
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2458,16 +2419,16 @@
         <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2479,7 +2440,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>9</v>
@@ -2488,7 +2449,7 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2547,16 +2508,16 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2636,16 +2597,16 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2660,13 +2621,13 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>10</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -2725,16 +2686,16 @@
         <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2749,7 +2710,7 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>8</v>
@@ -2814,16 +2775,16 @@
         <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2903,16 +2864,16 @@
         <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2933,7 +2894,7 @@
         <v>7</v>
       </c>
       <c r="AB27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -2992,16 +2953,16 @@
         <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -3081,16 +3042,16 @@
         <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -3102,16 +3063,16 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3170,16 +3131,16 @@
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3191,7 +3152,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>9</v>
@@ -3259,16 +3220,16 @@
         <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>10</v>
@@ -3348,16 +3309,16 @@
         <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3372,7 +3333,7 @@
         <v>8</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>9</v>
@@ -3437,16 +3398,16 @@
         <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3526,16 +3487,16 @@
         <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>9</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3550,7 +3511,7 @@
         <v>7</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>8</v>
@@ -3615,16 +3576,16 @@
         <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3639,13 +3600,13 @@
         <v>7</v>
       </c>
       <c r="Z35">
+        <v>6</v>
+      </c>
+      <c r="AA35">
+        <v>7</v>
+      </c>
+      <c r="AB35">
         <v>5</v>
-      </c>
-      <c r="AA35">
-        <v>7</v>
-      </c>
-      <c r="AB35">
-        <v>7</v>
       </c>
       <c r="AC35">
         <v>9</v>
@@ -3704,16 +3665,16 @@
         <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>8</v>
@@ -3725,7 +3686,7 @@
         <v>8</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z36">
         <v>8</v>
@@ -3734,7 +3695,7 @@
         <v>8</v>
       </c>
       <c r="AB36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC36">
         <v>8</v>
@@ -3793,16 +3754,16 @@
         <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>9</v>
@@ -3814,16 +3775,16 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>8</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC37">
         <v>9</v>
@@ -3882,16 +3843,16 @@
         <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>10</v>
@@ -3903,16 +3864,16 @@
         <v>9</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA38">
         <v>10</v>
       </c>
       <c r="AB38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC38">
         <v>10</v>
@@ -3971,16 +3932,16 @@
         <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -3992,16 +3953,16 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA39">
         <v>9</v>
       </c>
       <c r="AB39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC39">
         <v>10</v>
@@ -4259,7 +4220,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4318,16 +4279,16 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R6">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S6">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="T6">
         <v>100</v>
       </c>
       <c r="U6">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V6">
         <v>96.90000000000001</v>
@@ -4389,13 +4350,13 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>97</v>
+        <v>93.8</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4454,16 +4415,16 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R8">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="S8">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="T8">
         <v>100</v>
       </c>
       <c r="U8">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4599,7 +4560,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V10">
         <v>96.90000000000001</v>
@@ -4729,13 +4690,13 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T12">
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4803,7 +4764,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V13">
         <v>96.90000000000001</v>
@@ -4871,7 +4832,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4939,7 +4900,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4998,16 +4959,16 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="S16">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T16">
         <v>100</v>
       </c>
       <c r="U16">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="V16">
         <v>96.90000000000001</v>
@@ -5075,7 +5036,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>84.8</v>
+        <v>87.5</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5134,16 +5095,16 @@
         <v>95.3</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T18">
         <v>100</v>
       </c>
       <c r="U18">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5202,16 +5163,16 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S19">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T19">
         <v>100</v>
       </c>
       <c r="U19">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5270,7 +5231,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5279,7 +5240,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V20">
         <v>96.90000000000001</v>
@@ -5338,16 +5299,16 @@
         <v>98.40000000000001</v>
       </c>
       <c r="R21">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S21">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T21">
         <v>100</v>
       </c>
       <c r="U21">
-        <v>84.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V21">
         <v>96.90000000000001</v>
@@ -5415,7 +5376,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5483,7 +5444,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5619,7 +5580,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5678,10 +5639,10 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S26">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -5746,16 +5707,16 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T27">
         <v>100</v>
       </c>
       <c r="U27">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5823,7 +5784,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5882,16 +5843,16 @@
         <v>93.8</v>
       </c>
       <c r="R29">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S29">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="T29">
         <v>100</v>
       </c>
       <c r="U29">
-        <v>87.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5950,7 +5911,7 @@
         <v>95.3</v>
       </c>
       <c r="R30">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5959,7 +5920,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>90.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6222,16 +6183,16 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S34">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T34">
         <v>100</v>
       </c>
       <c r="U34">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6290,16 +6251,16 @@
         <v>98.40000000000001</v>
       </c>
       <c r="R35">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="S35">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="T35">
         <v>100</v>
       </c>
       <c r="U35">
-        <v>90.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="V35">
         <v>96.90000000000001</v>
@@ -6358,16 +6319,16 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="S36">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="T36">
         <v>100</v>
       </c>
       <c r="U36">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="V36">
         <v>90.59999999999999</v>
@@ -6426,16 +6387,16 @@
         <v>98.40000000000001</v>
       </c>
       <c r="R37">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="S37">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T37">
         <v>100</v>
       </c>
       <c r="U37">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V37">
         <v>100</v>
@@ -6503,7 +6464,7 @@
         <v>100</v>
       </c>
       <c r="U38">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V38">
         <v>100</v>
@@ -6562,16 +6523,16 @@
         <v>98.40000000000001</v>
       </c>
       <c r="R39">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T39">
         <v>100</v>
       </c>
       <c r="U39">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -6631,7 +6592,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6640,19 +6601,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6663,7 +6624,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -6672,19 +6633,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>88.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="G3" s="2">
-        <v>11.1</v>
+        <v>2.8</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6695,28 +6656,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6727,28 +6688,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6759,10 +6720,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>36</v>
@@ -6780,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6791,10 +6752,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>36</v>
@@ -6812,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6823,7 +6784,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
@@ -6844,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6914,7 +6875,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6946,22 +6907,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920105</v>
+        <v>23330051920097</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6972,19 +6933,19 @@
         <v>23330051920105</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" t="s">
         <v>80</v>
       </c>
-      <c r="D3" t="s">
-        <v>87</v>
-      </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6992,231 +6953,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920105</v>
+        <v>23330051920111</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>63</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920230</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920230</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920097</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920097</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920081</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920251</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920111</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920112</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920113</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>
